--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/157.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/157.xlsx
@@ -426,13 +426,13 @@
         <v>-15.07018978889758</v>
       </c>
       <c r="E2">
-        <v>-5.757798280870193</v>
+        <v>-5.857297911766726</v>
       </c>
       <c r="F2">
-        <v>-2.102812101725604</v>
+        <v>-2.789935379110274</v>
       </c>
       <c r="G2">
-        <v>-6.640554926436083</v>
+        <v>-7.904001457680157</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.87329518173893</v>
       </c>
       <c r="E3">
-        <v>-6.202562355533537</v>
+        <v>-5.969567839364889</v>
       </c>
       <c r="F3">
-        <v>-2.083581160794422</v>
+        <v>-2.738259846942443</v>
       </c>
       <c r="G3">
-        <v>-6.251234771017792</v>
+        <v>-6.513274382087724</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.52948945250369</v>
       </c>
       <c r="E4">
-        <v>-7.07318865435221</v>
+        <v>-6.731306980669128</v>
       </c>
       <c r="F4">
-        <v>-1.943192758067335</v>
+        <v>-2.478113978448697</v>
       </c>
       <c r="G4">
-        <v>-6.027322712923645</v>
+        <v>-7.0037780513683</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.03795303369845</v>
       </c>
       <c r="E5">
-        <v>-7.828298109709219</v>
+        <v>-7.761014042903252</v>
       </c>
       <c r="F5">
-        <v>-2.049670849733033</v>
+        <v>-2.320325398828677</v>
       </c>
       <c r="G5">
-        <v>-5.710205555716859</v>
+        <v>-7.107447784930577</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.38163919803688</v>
       </c>
       <c r="E6">
-        <v>-7.449192379683087</v>
+        <v>-8.481666339535897</v>
       </c>
       <c r="F6">
-        <v>-1.502190841442235</v>
+        <v>-2.104005424132887</v>
       </c>
       <c r="G6">
-        <v>-5.363813244306296</v>
+        <v>-7.184818544728884</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.57971962318822</v>
       </c>
       <c r="E7">
-        <v>-8.101134140197351</v>
+        <v>-8.943280865981784</v>
       </c>
       <c r="F7">
-        <v>-1.43034760629424</v>
+        <v>-2.061363350506722</v>
       </c>
       <c r="G7">
-        <v>-5.647540239203995</v>
+        <v>-6.886442385819912</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.64961997238107</v>
       </c>
       <c r="E8">
-        <v>-8.638134173448924</v>
+        <v>-9.326874313749515</v>
       </c>
       <c r="F8">
-        <v>-1.100060986511597</v>
+        <v>-1.896118683436812</v>
       </c>
       <c r="G8">
-        <v>-5.849546417464783</v>
+        <v>-7.314707798962189</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.62421799482003</v>
       </c>
       <c r="E9">
-        <v>-9.073945454999103</v>
+        <v>-9.811253479031961</v>
       </c>
       <c r="F9">
-        <v>-0.7011508057070474</v>
+        <v>-1.641414428468517</v>
       </c>
       <c r="G9">
-        <v>-5.437012716725122</v>
+        <v>-6.687366040361378</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.546077275262675</v>
       </c>
       <c r="E10">
-        <v>-9.788615637467617</v>
+        <v>-10.67056764977947</v>
       </c>
       <c r="F10">
-        <v>-0.7463766955342517</v>
+        <v>-1.608109093066826</v>
       </c>
       <c r="G10">
-        <v>-5.192439543920385</v>
+        <v>-6.069568584550285</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.456221460707312</v>
       </c>
       <c r="E11">
-        <v>-10.79729246641012</v>
+        <v>-11.04113720630115</v>
       </c>
       <c r="F11">
-        <v>-0.4903049105079742</v>
+        <v>-1.376585541582817</v>
       </c>
       <c r="G11">
-        <v>-5.682327451730656</v>
+        <v>-5.253380066207288</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.410639624645273</v>
       </c>
       <c r="E12">
-        <v>-10.9258060302738</v>
+        <v>-11.89526174583587</v>
       </c>
       <c r="F12">
-        <v>-0.2955565940863853</v>
+        <v>-1.585210289235486</v>
       </c>
       <c r="G12">
-        <v>-4.71459871132752</v>
+        <v>-6.707269040143476</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.442664442929678</v>
       </c>
       <c r="E13">
-        <v>-11.49256719470378</v>
+        <v>-12.4552618985724</v>
       </c>
       <c r="F13">
-        <v>-0.1065476279023491</v>
+        <v>-1.139236327888865</v>
       </c>
       <c r="G13">
-        <v>-4.575019490300769</v>
+        <v>-5.146297160194022</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.589390419080792</v>
       </c>
       <c r="E14">
-        <v>-11.61170681737158</v>
+        <v>-13.4554342533285</v>
       </c>
       <c r="F14">
-        <v>0.1999010504410994</v>
+        <v>-0.4595002467467615</v>
       </c>
       <c r="G14">
-        <v>-4.227326134493273</v>
+        <v>-5.414941309614801</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.867697272119431</v>
       </c>
       <c r="E15">
-        <v>-13.23925396115033</v>
+        <v>-13.85812427598658</v>
       </c>
       <c r="F15">
-        <v>0.2852311251649769</v>
+        <v>-0.7161524599910475</v>
       </c>
       <c r="G15">
-        <v>-3.883181683503876</v>
+        <v>-4.043335945057199</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.289986889031606</v>
       </c>
       <c r="E16">
-        <v>-13.8322802748248</v>
+        <v>-14.62501682071154</v>
       </c>
       <c r="F16">
-        <v>0.7097933825348571</v>
+        <v>-0.5428926572830988</v>
       </c>
       <c r="G16">
-        <v>-3.917118085826945</v>
+        <v>-3.519855931659942</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.869746334655319</v>
       </c>
       <c r="E17">
-        <v>-14.46165664935884</v>
+        <v>-15.76871463066674</v>
       </c>
       <c r="F17">
-        <v>1.22708399681259</v>
+        <v>-0.102880556855149</v>
       </c>
       <c r="G17">
-        <v>-3.590201713823915</v>
+        <v>-4.200550442171648</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.604292346214129</v>
       </c>
       <c r="E18">
-        <v>-15.10557395393151</v>
+        <v>-16.51480336580047</v>
       </c>
       <c r="F18">
-        <v>1.588571206835306</v>
+        <v>0.2948299667184553</v>
       </c>
       <c r="G18">
-        <v>-3.665824505577487</v>
+        <v>-3.067013028434115</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.489396418631178</v>
       </c>
       <c r="E19">
-        <v>-16.73220181748671</v>
+        <v>-16.49884502339744</v>
       </c>
       <c r="F19">
-        <v>1.786045081137366</v>
+        <v>0.6927305350019125</v>
       </c>
       <c r="G19">
-        <v>-3.416901275934147</v>
+        <v>-3.064060021813085</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.503508761834617</v>
       </c>
       <c r="E20">
-        <v>-15.88175892732022</v>
+        <v>-17.45871848795928</v>
       </c>
       <c r="F20">
-        <v>2.154742904193077</v>
+        <v>1.150177653852935</v>
       </c>
       <c r="G20">
-        <v>-3.030918150419441</v>
+        <v>-2.719243530079216</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.625949997817162</v>
       </c>
       <c r="E21">
-        <v>-17.0815917010745</v>
+        <v>-18.05246935747498</v>
       </c>
       <c r="F21">
-        <v>2.545215099880166</v>
+        <v>1.059067052537704</v>
       </c>
       <c r="G21">
-        <v>-2.940046985911986</v>
+        <v>-2.182885494534194</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.834404724578111</v>
       </c>
       <c r="E22">
-        <v>-17.54020837772731</v>
+        <v>-17.83851254603458</v>
       </c>
       <c r="F22">
-        <v>2.676485315799111</v>
+        <v>1.49629183055448</v>
       </c>
       <c r="G22">
-        <v>-2.889349291523587</v>
+        <v>-1.642736884346707</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.105856372645544</v>
       </c>
       <c r="E23">
-        <v>-19.33789934692225</v>
+        <v>-18.98771698038311</v>
       </c>
       <c r="F23">
-        <v>2.734876552901363</v>
+        <v>1.40651787703188</v>
       </c>
       <c r="G23">
-        <v>-2.033940740176845</v>
+        <v>-1.174668782185772</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.427188828982749</v>
       </c>
       <c r="E24">
-        <v>-18.37425366351203</v>
+        <v>-19.86550279660791</v>
       </c>
       <c r="F24">
-        <v>3.054226099631981</v>
+        <v>1.728950899179858</v>
       </c>
       <c r="G24">
-        <v>-2.063791929304453</v>
+        <v>-1.955298730891457</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.785606261355415</v>
       </c>
       <c r="E25">
-        <v>-18.99248093503918</v>
+        <v>-19.53113386130356</v>
       </c>
       <c r="F25">
-        <v>3.307520856335536</v>
+        <v>2.106789872779486</v>
       </c>
       <c r="G25">
-        <v>-2.72231240579412</v>
+        <v>-2.717733921313308</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.173043699855317</v>
       </c>
       <c r="E26">
-        <v>-19.40612533632181</v>
+        <v>-19.89139208250976</v>
       </c>
       <c r="F26">
-        <v>2.865654236280606</v>
+        <v>1.79024190181328</v>
       </c>
       <c r="G26">
-        <v>-2.27938789700395</v>
+        <v>-2.639340202943366</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.587523493431646</v>
       </c>
       <c r="E27">
-        <v>-18.46291212763419</v>
+        <v>-20.27225938892488</v>
       </c>
       <c r="F27">
-        <v>3.341852433170432</v>
+        <v>1.639647306314143</v>
       </c>
       <c r="G27">
-        <v>-2.453757641102902</v>
+        <v>-1.740351630117658</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.021751549312839</v>
       </c>
       <c r="E28">
-        <v>-18.82932907349083</v>
+        <v>-20.54945181140839</v>
       </c>
       <c r="F28">
-        <v>3.181430942465993</v>
+        <v>1.887140948249443</v>
       </c>
       <c r="G28">
-        <v>-2.322997713392769</v>
+        <v>-3.31863435269196</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.477607338938079</v>
       </c>
       <c r="E29">
-        <v>-18.28374758199472</v>
+        <v>-20.13178612520694</v>
       </c>
       <c r="F29">
-        <v>3.291954610892681</v>
+        <v>2.045019007253686</v>
       </c>
       <c r="G29">
-        <v>-3.056204097248394</v>
+        <v>-3.21048214046951</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.948732509957543</v>
       </c>
       <c r="E30">
-        <v>-18.44881951652232</v>
+        <v>-20.56837630428644</v>
       </c>
       <c r="F30">
-        <v>2.978825860997909</v>
+        <v>1.854610045040401</v>
       </c>
       <c r="G30">
-        <v>-2.927188827037457</v>
+        <v>-2.870101779758265</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.43142657349973</v>
       </c>
       <c r="E31">
-        <v>-18.69206649784434</v>
+        <v>-19.61440796983061</v>
       </c>
       <c r="F31">
-        <v>3.042904186042505</v>
+        <v>1.66560266256228</v>
       </c>
       <c r="G31">
-        <v>-2.888349506770727</v>
+        <v>-2.686194353960671</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.916766042539601</v>
       </c>
       <c r="E32">
-        <v>-17.52535045450815</v>
+        <v>-18.94046688258708</v>
       </c>
       <c r="F32">
-        <v>2.970980181892822</v>
+        <v>1.774157784536077</v>
       </c>
       <c r="G32">
-        <v>-2.665688834890426</v>
+        <v>-3.456843007865454</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.389275991700854</v>
       </c>
       <c r="E33">
-        <v>-17.5408514210364</v>
+        <v>-17.96673175908776</v>
       </c>
       <c r="F33">
-        <v>2.818290343467559</v>
+        <v>1.663711717699246</v>
       </c>
       <c r="G33">
-        <v>-3.657577936639163</v>
+        <v>-2.743456860153445</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.837967354897835</v>
       </c>
       <c r="E34">
-        <v>-17.08969314107423</v>
+        <v>-18.94229185761217</v>
       </c>
       <c r="F34">
-        <v>2.703927771901845</v>
+        <v>1.536516377100727</v>
       </c>
       <c r="G34">
-        <v>-2.706689941394299</v>
+        <v>-3.323888188462784</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.242033479351058</v>
       </c>
       <c r="E35">
-        <v>-16.97519067579028</v>
+        <v>-18.25222487442733</v>
       </c>
       <c r="F35">
-        <v>2.469924136954259</v>
+        <v>1.222046228295577</v>
       </c>
       <c r="G35">
-        <v>-3.16551168986405</v>
+        <v>-3.433364618900943</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.589943566070135</v>
       </c>
       <c r="E36">
-        <v>-16.90808774794462</v>
+        <v>-18.10575591112324</v>
       </c>
       <c r="F36">
-        <v>2.396489277361247</v>
+        <v>1.268572340679357</v>
       </c>
       <c r="G36">
-        <v>-3.51586672428512</v>
+        <v>-2.501704272148167</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.865918418497113</v>
       </c>
       <c r="E37">
-        <v>-15.19209044984806</v>
+        <v>-16.41779439560816</v>
       </c>
       <c r="F37">
-        <v>2.340118849007096</v>
+        <v>1.066329927865909</v>
       </c>
       <c r="G37">
-        <v>-2.842392513594564</v>
+        <v>-3.378336730947177</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.06587535797753</v>
       </c>
       <c r="E38">
-        <v>-15.11896012309819</v>
+        <v>-16.4979348001219</v>
       </c>
       <c r="F38">
-        <v>2.274604102697197</v>
+        <v>0.9300425316068519</v>
       </c>
       <c r="G38">
-        <v>-2.995144395322076</v>
+        <v>-3.834092914247563</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.18948089335442</v>
       </c>
       <c r="E39">
-        <v>-14.68028684597516</v>
+        <v>-16.47613472624898</v>
       </c>
       <c r="F39">
-        <v>2.323782922489338</v>
+        <v>1.384933549110355</v>
       </c>
       <c r="G39">
-        <v>-3.113195138706948</v>
+        <v>-2.771487249234454</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.24142165399122</v>
       </c>
       <c r="E40">
-        <v>-14.70613537561094</v>
+        <v>-15.83507941724915</v>
       </c>
       <c r="F40">
-        <v>2.045587557677329</v>
+        <v>1.177767394605806</v>
       </c>
       <c r="G40">
-        <v>-3.189463486840677</v>
+        <v>-3.049053318883568</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.23606707067115</v>
       </c>
       <c r="E41">
-        <v>-13.91679065675594</v>
+        <v>-15.58111353795099</v>
       </c>
       <c r="F41">
-        <v>2.50960547237151</v>
+        <v>0.9349805266511921</v>
       </c>
       <c r="G41">
-        <v>-2.700519084509098</v>
+        <v>-2.376856978771172</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.18430280998274</v>
       </c>
       <c r="E42">
-        <v>-14.94172470738599</v>
+        <v>-14.03223051615948</v>
       </c>
       <c r="F42">
-        <v>2.280756800178679</v>
+        <v>0.8133044011679794</v>
       </c>
       <c r="G42">
-        <v>-3.488051520664163</v>
+        <v>-2.46153411257465</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.10452242957061</v>
       </c>
       <c r="E43">
-        <v>-14.04639105438146</v>
+        <v>-15.21095607256401</v>
       </c>
       <c r="F43">
-        <v>2.308156496221696</v>
+        <v>1.246783714694741</v>
       </c>
       <c r="G43">
-        <v>-2.450013414097986</v>
+        <v>-2.307441459903734</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.00582043755074</v>
       </c>
       <c r="E44">
-        <v>-11.94265222632614</v>
+        <v>-13.07925844598533</v>
       </c>
       <c r="F44">
-        <v>2.236476382782992</v>
+        <v>0.7077646552571791</v>
       </c>
       <c r="G44">
-        <v>-1.790810965227229</v>
+        <v>-2.325523659639233</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.900800393899184</v>
       </c>
       <c r="E45">
-        <v>-12.3571977939363</v>
+        <v>-14.23545031572769</v>
       </c>
       <c r="F45">
-        <v>2.037648439923231</v>
+        <v>0.9005887689915091</v>
       </c>
       <c r="G45">
-        <v>-2.127539794208658</v>
+        <v>-1.780501926417939</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.791521835412354</v>
       </c>
       <c r="E46">
-        <v>-11.66325443700089</v>
+        <v>-12.45631250454218</v>
       </c>
       <c r="F46">
-        <v>2.232214630164544</v>
+        <v>0.8574296153839532</v>
       </c>
       <c r="G46">
-        <v>-2.449215572623022</v>
+        <v>-2.356232280061512</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.6796274882043</v>
       </c>
       <c r="E47">
-        <v>-11.36463780398709</v>
+        <v>-12.36974619541155</v>
       </c>
       <c r="F47">
-        <v>2.174072034891016</v>
+        <v>0.9347081292337366</v>
       </c>
       <c r="G47">
-        <v>-2.258902241206939</v>
+        <v>-2.186205971710083</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.56429663779501</v>
       </c>
       <c r="E48">
-        <v>-10.5845628714258</v>
+        <v>-12.10300549093775</v>
       </c>
       <c r="F48">
-        <v>1.670369617367753</v>
+        <v>0.6769061454948415</v>
       </c>
       <c r="G48">
-        <v>-1.800140082556895</v>
+        <v>-2.637830594177458</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.439107700652917</v>
       </c>
       <c r="E49">
-        <v>-9.908561328508782</v>
+        <v>-11.1693428339323</v>
       </c>
       <c r="F49">
-        <v>1.580796794496413</v>
+        <v>0.5513166826945779</v>
       </c>
       <c r="G49">
-        <v>-1.636645480554448</v>
+        <v>-3.339000828849557</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.30196678697413</v>
       </c>
       <c r="E50">
-        <v>-9.210809524932925</v>
+        <v>-10.71017368345056</v>
       </c>
       <c r="F50">
-        <v>1.67323929248653</v>
+        <v>0.7905275426921292</v>
       </c>
       <c r="G50">
-        <v>-1.386298716329222</v>
+        <v>-2.367822499994501</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.144196537676436</v>
       </c>
       <c r="E51">
-        <v>-9.326675060893178</v>
+        <v>-10.66816755855541</v>
       </c>
       <c r="F51">
-        <v>1.410352029053158</v>
+        <v>0.2016890544196306</v>
       </c>
       <c r="G51">
-        <v>-1.429633757438282</v>
+        <v>-2.214183392062464</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.966772334360531</v>
       </c>
       <c r="E52">
-        <v>-9.51059903271471</v>
+        <v>-11.52923877721789</v>
       </c>
       <c r="F52">
-        <v>1.248283484196663</v>
+        <v>0.4067069118498865</v>
       </c>
       <c r="G52">
-        <v>-1.463308626663748</v>
+        <v>-1.250198878664244</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.764849904258629</v>
       </c>
       <c r="E53">
-        <v>-9.186500676459751</v>
+        <v>-10.83119262283154</v>
       </c>
       <c r="F53">
-        <v>1.29067454043523</v>
+        <v>0.3657744487594385</v>
       </c>
       <c r="G53">
-        <v>-1.319193958248195</v>
+        <v>-1.657303284719501</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.541761421694755</v>
       </c>
       <c r="E54">
-        <v>-7.486864754952896</v>
+        <v>-9.984540065409474</v>
       </c>
       <c r="F54">
-        <v>1.297245336278388</v>
+        <v>0.2246440798109677</v>
       </c>
       <c r="G54">
-        <v>-1.925526994856791</v>
+        <v>-1.995343089734481</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.301547722848261</v>
       </c>
       <c r="E55">
-        <v>-7.944435354109933</v>
+        <v>-8.884107296123554</v>
       </c>
       <c r="F55">
-        <v>0.9276638053218619</v>
+        <v>0.04004019163072618</v>
       </c>
       <c r="G55">
-        <v>-1.199451526092756</v>
+        <v>-1.773755034608904</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.048643814481483</v>
       </c>
       <c r="E56">
-        <v>-8.434869089140632</v>
+        <v>-7.911463534860085</v>
       </c>
       <c r="F56">
-        <v>1.126797403423303</v>
+        <v>-0.07084852100947077</v>
       </c>
       <c r="G56">
-        <v>-1.526659226103242</v>
+        <v>-1.958036552052435</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.794754573246983</v>
       </c>
       <c r="E57">
-        <v>-8.283006713293407</v>
+        <v>-8.125556200520716</v>
       </c>
       <c r="F57">
-        <v>1.153289635976774</v>
+        <v>0.6907604048431059</v>
       </c>
       <c r="G57">
-        <v>-1.960390349930856</v>
+        <v>-1.754805471942116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.54663322588864</v>
       </c>
       <c r="E58">
-        <v>-7.996327137763827</v>
+        <v>-7.808748687418105</v>
       </c>
       <c r="F58">
-        <v>1.187994967407714</v>
+        <v>0.2542530456060236</v>
       </c>
       <c r="G58">
-        <v>-1.726748598496792</v>
+        <v>-2.619344507886169</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.318883948099752</v>
       </c>
       <c r="E59">
-        <v>-7.236784306353309</v>
+        <v>-7.068782449142746</v>
       </c>
       <c r="F59">
-        <v>0.9488632927059343</v>
+        <v>0.2614953327573282</v>
       </c>
       <c r="G59">
-        <v>-1.091113923320107</v>
+        <v>-1.979333291506566</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.117802589795353</v>
       </c>
       <c r="E60">
-        <v>-7.967521514601036</v>
+        <v>-7.035692889568699</v>
       </c>
       <c r="F60">
-        <v>0.8680151057227505</v>
+        <v>-0.0864147664523251</v>
       </c>
       <c r="G60">
-        <v>-2.089114292134338</v>
+        <v>-1.991837222008393</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.953682506388436</v>
       </c>
       <c r="E61">
-        <v>-7.295849192835353</v>
+        <v>-6.503669649251554</v>
       </c>
       <c r="F61">
-        <v>0.6732541196538382</v>
+        <v>0.3644853121442709</v>
       </c>
       <c r="G61">
-        <v>-1.805632277606546</v>
+        <v>-2.551819310521654</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.832048703192799</v>
       </c>
       <c r="E62">
-        <v>-6.563083228232189</v>
+        <v>-7.251388635028046</v>
       </c>
       <c r="F62">
-        <v>0.8156736252174768</v>
+        <v>-0.4058031139778716</v>
       </c>
       <c r="G62">
-        <v>-2.13702781772421</v>
+        <v>-2.748455783917745</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.750406393292195</v>
       </c>
       <c r="E63">
-        <v>-6.664176881979423</v>
+        <v>-6.732584010339291</v>
       </c>
       <c r="F63">
-        <v>0.557984084598578</v>
+        <v>-0.1239691848251407</v>
       </c>
       <c r="G63">
-        <v>-1.897182103949552</v>
+        <v>-3.575102315619299</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.705514513364503</v>
       </c>
       <c r="E64">
-        <v>-6.835869445506237</v>
+        <v>-6.135137906033333</v>
       </c>
       <c r="F64">
-        <v>0.4787631554435082</v>
+        <v>-0.5191378604044647</v>
       </c>
       <c r="G64">
-        <v>-1.73043985677308</v>
+        <v>-1.945333988818251</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.682666195455828</v>
       </c>
       <c r="E65">
-        <v>-6.297963717453128</v>
+        <v>-5.933919691976508</v>
       </c>
       <c r="F65">
-        <v>0.7268625648914635</v>
+        <v>-0.05424019707425728</v>
       </c>
       <c r="G65">
-        <v>-1.738517587888901</v>
+        <v>-2.166922043943829</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.670301538295385</v>
       </c>
       <c r="E66">
-        <v>-6.700531471313</v>
+        <v>-7.012987120894239</v>
       </c>
       <c r="F66">
-        <v>0.724064156538882</v>
+        <v>-0.127491346781078</v>
       </c>
       <c r="G66">
-        <v>-1.738090527514335</v>
+        <v>-3.130909867887588</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.648476822065782</v>
       </c>
       <c r="E67">
-        <v>-6.788288769107644</v>
+        <v>-6.293865448476187</v>
       </c>
       <c r="F67">
-        <v>0.3619244596790053</v>
+        <v>-0.1722310388922424</v>
       </c>
       <c r="G67">
-        <v>-2.342976855722271</v>
+        <v>-2.593479215587843</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.602912026824227</v>
       </c>
       <c r="E68">
-        <v>-6.076082076499304</v>
+        <v>-5.291791134636867</v>
       </c>
       <c r="F68">
-        <v>0.3487860354045196</v>
+        <v>-0.875599971557491</v>
       </c>
       <c r="G68">
-        <v>-2.218798292544208</v>
+        <v>-3.00475490902258</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.519376844608991</v>
       </c>
       <c r="E69">
-        <v>-6.996530646350365</v>
+        <v>-5.955928075653786</v>
       </c>
       <c r="F69">
-        <v>0.1335928674675652</v>
+        <v>-0.7424110959219913</v>
       </c>
       <c r="G69">
-        <v>-1.825591556662812</v>
+        <v>-2.683648544440972</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.385503432581284</v>
       </c>
       <c r="E70">
-        <v>-6.307672765725574</v>
+        <v>-7.373643847813122</v>
       </c>
       <c r="F70">
-        <v>0.05126470730640326</v>
+        <v>-1.282862617360069</v>
       </c>
       <c r="G70">
-        <v>-1.808972618055671</v>
+        <v>-2.566524753807097</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.197389653869136</v>
       </c>
       <c r="E71">
-        <v>-5.397929508428645</v>
+        <v>-6.164568458609183</v>
       </c>
       <c r="F71">
-        <v>0.3211250278854542</v>
+        <v>-0.744963238004722</v>
       </c>
       <c r="G71">
-        <v>-1.240333452957216</v>
+        <v>-2.346853504548757</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.950697294854036</v>
       </c>
       <c r="E72">
-        <v>-7.170401405874869</v>
+        <v>-7.149538726121532</v>
       </c>
       <c r="F72">
-        <v>-0.007445646537810214</v>
+        <v>-0.560959574366432</v>
       </c>
       <c r="G72">
-        <v>-1.497423798445938</v>
+        <v>-2.457968655028855</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.652072037480084</v>
       </c>
       <c r="E73">
-        <v>-6.845619250044751</v>
+        <v>-6.907387635509375</v>
       </c>
       <c r="F73">
-        <v>-0.2136750389933773</v>
+        <v>-0.7150232776733392</v>
       </c>
       <c r="G73">
-        <v>-1.777750863074804</v>
+        <v>-2.579217385404662</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.305610158684058</v>
       </c>
       <c r="E74">
-        <v>-7.349425568820101</v>
+        <v>-6.844681855925163</v>
       </c>
       <c r="F74">
-        <v>-0.01248895802552713</v>
+        <v>-1.298131917943778</v>
       </c>
       <c r="G74">
-        <v>-1.350902363423335</v>
+        <v>-1.838962850095929</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.924027853928079</v>
       </c>
       <c r="E75">
-        <v>-7.649133564069748</v>
+        <v>-6.558088321401729</v>
       </c>
       <c r="F75">
-        <v>-0.0002073186512942194</v>
+        <v>-0.7856819007965855</v>
       </c>
       <c r="G75">
-        <v>-1.12643744422413</v>
+        <v>-1.846686352839048</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.518767306954772</v>
       </c>
       <c r="E76">
-        <v>-7.907691316011695</v>
+        <v>-7.496759470659656</v>
       </c>
       <c r="F76">
-        <v>0.01258981699841424</v>
+        <v>-0.9799891551207245</v>
       </c>
       <c r="G76">
-        <v>-0.9401100096373299</v>
+        <v>-2.925096562256637</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.101138313744126</v>
       </c>
       <c r="E77">
-        <v>-9.087861455624674</v>
+        <v>-8.751667545295227</v>
       </c>
       <c r="F77">
-        <v>-0.2983415409386856</v>
+        <v>-0.7611067442537539</v>
       </c>
       <c r="G77">
-        <v>-1.213905367917214</v>
+        <v>-2.292471172975149</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.684649943559776</v>
       </c>
       <c r="E78">
-        <v>-8.964963199530509</v>
+        <v>-9.236001425837594</v>
       </c>
       <c r="F78">
-        <v>-0.3064105225778496</v>
+        <v>-1.141201706929925</v>
       </c>
       <c r="G78">
-        <v>-0.3041012428147066</v>
+        <v>-1.646567185535644</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.27576507948543</v>
       </c>
       <c r="E79">
-        <v>-9.893155459934686</v>
+        <v>-9.685615496163154</v>
       </c>
       <c r="F79">
-        <v>-0.4113864691827534</v>
+        <v>-1.082542823527964</v>
       </c>
       <c r="G79">
-        <v>-0.30985497096196</v>
+        <v>-1.801858255691777</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.885542409243159</v>
       </c>
       <c r="E80">
-        <v>-9.914475515562799</v>
+        <v>-10.24524431403106</v>
       </c>
       <c r="F80">
-        <v>-0.2231614374268596</v>
+        <v>-1.015065865588835</v>
       </c>
       <c r="G80">
-        <v>-0.4505597774720639</v>
+        <v>-0.5796909167768759</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.517079000396076</v>
       </c>
       <c r="E81">
-        <v>-10.6925488626127</v>
+        <v>-11.15161838666628</v>
       </c>
       <c r="F81">
-        <v>-0.09163466114961352</v>
+        <v>-1.305976805195907</v>
       </c>
       <c r="G81">
-        <v>-0.7496940513095298</v>
+        <v>-1.195703988542301</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.177641766448615</v>
       </c>
       <c r="E82">
-        <v>-12.45534341110454</v>
+        <v>-10.47690745884145</v>
       </c>
       <c r="F82">
-        <v>-0.4493653207409068</v>
+        <v>-1.108785622399753</v>
       </c>
       <c r="G82">
-        <v>0.4669215027360136</v>
+        <v>-0.1404709084451496</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.871776211347148</v>
       </c>
       <c r="E83">
-        <v>-13.17155780320967</v>
+        <v>-13.28659915690052</v>
       </c>
       <c r="F83">
-        <v>-0.4646021553533497</v>
+        <v>-1.53688746249064</v>
       </c>
       <c r="G83">
-        <v>0.380973119445455</v>
+        <v>-0.5492769349075914</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.603179179977819</v>
       </c>
       <c r="E84">
-        <v>-13.76952921050051</v>
+        <v>-13.3205944112761</v>
       </c>
       <c r="F84">
-        <v>-0.3448819066757047</v>
+        <v>-1.316502114709918</v>
       </c>
       <c r="G84">
-        <v>0.909624204975053</v>
+        <v>-0.6588692344396249</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.378674735972593</v>
       </c>
       <c r="E85">
-        <v>-14.80345228203578</v>
+        <v>-15.29322485986136</v>
       </c>
       <c r="F85">
-        <v>-0.4848292473053423</v>
+        <v>-0.8527732263453046</v>
       </c>
       <c r="G85">
-        <v>1.047015155400347</v>
+        <v>-0.9531005903334301</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.201602610565515</v>
       </c>
       <c r="E86">
-        <v>-16.51165607636515</v>
+        <v>-15.13525357257778</v>
       </c>
       <c r="F86">
-        <v>-0.621567207897342</v>
+        <v>-1.658799560155254</v>
       </c>
       <c r="G86">
-        <v>0.5800958125415384</v>
+        <v>0.0005980580742741712</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.078691122510782</v>
       </c>
       <c r="E87">
-        <v>-18.16834395038325</v>
+        <v>-17.96431808244167</v>
       </c>
       <c r="F87">
-        <v>-0.9686656578253324</v>
+        <v>-1.67200370822523</v>
       </c>
       <c r="G87">
-        <v>1.707227320660582</v>
+        <v>0.3208337491790547</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.014843901526252</v>
       </c>
       <c r="E88">
-        <v>-19.14736833152353</v>
+        <v>-19.62742280412865</v>
       </c>
       <c r="F88">
-        <v>-0.6352227121532186</v>
+        <v>-1.744570696976581</v>
       </c>
       <c r="G88">
-        <v>0.9524130060701331</v>
+        <v>0.1521316590433342</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.014043321132162</v>
       </c>
       <c r="E89">
-        <v>-20.4758414664137</v>
+        <v>-19.72841683144771</v>
       </c>
       <c r="F89">
-        <v>-0.80651951137898</v>
+        <v>-1.900602946736379</v>
       </c>
       <c r="G89">
-        <v>1.473774270322256</v>
+        <v>-0.3875898907695867</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.080549344460246</v>
       </c>
       <c r="E90">
-        <v>-21.93552713567613</v>
+        <v>-21.7535504076779</v>
       </c>
       <c r="F90">
-        <v>-0.814020734447459</v>
+        <v>-1.513723387918465</v>
       </c>
       <c r="G90">
-        <v>0.715937427654453</v>
+        <v>0.2916777746146933</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.213909016138078</v>
       </c>
       <c r="E91">
-        <v>-24.09674135583681</v>
+        <v>-23.65879263455501</v>
       </c>
       <c r="F91">
-        <v>-1.067669449423114</v>
+        <v>-1.593561962380557</v>
       </c>
       <c r="G91">
-        <v>1.031644292461511</v>
+        <v>0.5883490025709415</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.413579395709026</v>
       </c>
       <c r="E92">
-        <v>-25.70141517740282</v>
+        <v>-26.31490566511795</v>
       </c>
       <c r="F92">
-        <v>-1.373088718921527</v>
+        <v>-1.871002691323858</v>
       </c>
       <c r="G92">
-        <v>0.6515738012799426</v>
+        <v>-0.2764019082876246</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.676909545114931</v>
       </c>
       <c r="E93">
-        <v>-28.4679595751168</v>
+        <v>-26.91440316814938</v>
       </c>
       <c r="F93">
-        <v>-1.029400779682435</v>
+        <v>-2.183887550507653</v>
       </c>
       <c r="G93">
-        <v>1.334559209304824</v>
+        <v>-0.2367978520013234</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.997361815600314</v>
       </c>
       <c r="E94">
-        <v>-29.93964796473656</v>
+        <v>-30.11924271540676</v>
       </c>
       <c r="F94">
-        <v>-1.391365477038656</v>
+        <v>-2.359731169416641</v>
       </c>
       <c r="G94">
-        <v>0.7968802660896335</v>
+        <v>0.7680553460791993</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.370252486216198</v>
       </c>
       <c r="E95">
-        <v>-32.70678106407155</v>
+        <v>-33.00277571063491</v>
       </c>
       <c r="F95">
-        <v>-1.228741051405841</v>
+        <v>-2.202036820298589</v>
       </c>
       <c r="G95">
-        <v>0.3751697331151126</v>
+        <v>0.6223681685324922</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.79003282135898</v>
       </c>
       <c r="E96">
-        <v>-34.49378030613438</v>
+        <v>-34.7181435508444</v>
       </c>
       <c r="F96">
-        <v>-1.09146542265555</v>
+        <v>-1.766349028872747</v>
       </c>
       <c r="G96">
-        <v>0.4502793903100973</v>
+        <v>0.3858131370238695</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.243009613686956</v>
       </c>
       <c r="E97">
-        <v>-37.56570008431861</v>
+        <v>-37.34626608356594</v>
       </c>
       <c r="F97">
-        <v>-1.811296978311791</v>
+        <v>-2.160969742205328</v>
       </c>
       <c r="G97">
-        <v>-0.3939064116585161</v>
+        <v>-0.768653545612936</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.73254966088811</v>
       </c>
       <c r="E98">
-        <v>-39.61388812172185</v>
+        <v>-38.42615543051606</v>
       </c>
       <c r="F98">
-        <v>-1.621055097072585</v>
+        <v>-2.204348239082173</v>
       </c>
       <c r="G98">
-        <v>-0.2940603581940971</v>
+        <v>-0.2810068771327508</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.228678251189157</v>
       </c>
       <c r="E99">
-        <v>-42.42307715916607</v>
+        <v>-42.37252580381845</v>
       </c>
       <c r="F99">
-        <v>-1.755921117272536</v>
+        <v>-2.637273255538531</v>
       </c>
       <c r="G99">
-        <v>-0.4033911246285281</v>
+        <v>-1.66489436564105</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.756143564697791</v>
       </c>
       <c r="E100">
-        <v>-44.70846213661707</v>
+        <v>-43.68541645964823</v>
       </c>
       <c r="F100">
-        <v>-2.038318845731163</v>
+        <v>-2.652974115984198</v>
       </c>
       <c r="G100">
-        <v>-0.9561562238661774</v>
+        <v>-1.515949611283699</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.250236456886017</v>
       </c>
       <c r="E101">
-        <v>-47.16137348150782</v>
+        <v>-46.04145921704091</v>
       </c>
       <c r="F101">
-        <v>-2.039085359394235</v>
+        <v>-2.308350998402039</v>
       </c>
       <c r="G101">
-        <v>-1.56932222646783</v>
+        <v>-1.528086071230668</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.793012382676557</v>
       </c>
       <c r="E102">
-        <v>-48.92033354463366</v>
+        <v>-47.75206989530535</v>
       </c>
       <c r="F102">
-        <v>-2.228407107496571</v>
+        <v>-2.967164740695272</v>
       </c>
       <c r="G102">
-        <v>-1.886128192393925</v>
+        <v>-1.904750011052325</v>
       </c>
     </row>
   </sheetData>
